--- a/amostras/principal/P10/matriz_rastreabilidade_P10.xlsx
+++ b/amostras/principal/P10/matriz_rastreabilidade_P10.xlsx
@@ -874,6 +874,7 @@
           <t>Nenhuma</t>
         </is>
       </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>Nenhum</t>
@@ -931,6 +932,7 @@
           <t>Nenhuma</t>
         </is>
       </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>Nenhum</t>
@@ -988,6 +990,7 @@
           <t>Nenhuma</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
           <t>Nenhum</t>
@@ -1045,6 +1048,7 @@
           <t>Nenhuma</t>
         </is>
       </c>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t>Nenhum</t>
@@ -1102,6 +1106,7 @@
           <t>Nenhuma</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
           <t>Nenhum</t>
@@ -1159,6 +1164,7 @@
           <t>Nenhuma</t>
         </is>
       </c>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>Nenhum</t>
@@ -1216,6 +1222,7 @@
           <t>Nenhuma</t>
         </is>
       </c>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>Nenhum</t>
@@ -1273,6 +1280,7 @@
           <t>Nenhuma</t>
         </is>
       </c>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>Nenhum</t>
@@ -1330,6 +1338,7 @@
           <t>Nenhuma</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>Nenhum</t>
@@ -1567,6 +1576,7 @@
           <t>Nenhuma</t>
         </is>
       </c>
+      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
           <t>Nenhum</t>
@@ -1804,6 +1814,7 @@
           <t>Nenhuma</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
           <t>Nenhum</t>
@@ -1861,6 +1872,7 @@
           <t>Nenhuma</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>Nenhum</t>
@@ -1918,6 +1930,7 @@
           <t>Nenhuma</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
           <t>Nenhum</t>
